--- a/baselines/svm-baseline/detected_events.xlsx
+++ b/baselines/svm-baseline/detected_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,49 +435,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="B2" t="n">
-        <v>95.5</v>
+        <v>46</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99</v>
+        <v>48.5</v>
       </c>
       <c r="B3" t="n">
-        <v>99.5</v>
+        <v>55</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="B4" t="n">
-        <v>203</v>
+        <v>114.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>212</v>
+        <v>117.5</v>
       </c>
       <c r="B5" t="n">
-        <v>212</v>
+        <v>118.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -487,66 +487,274 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>213.5</v>
+        <v>122</v>
       </c>
       <c r="B6" t="n">
-        <v>294.5</v>
+        <v>123.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>295</v>
+        <v>128.5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>128.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>295.5</v>
+        <v>129</v>
       </c>
       <c r="B8" t="n">
-        <v>296.5</v>
+        <v>131.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>297.5</v>
+        <v>134.5</v>
       </c>
       <c r="B9" t="n">
-        <v>297.5</v>
+        <v>145.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>299</v>
+        <v>147.5</v>
       </c>
       <c r="B10" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>152</v>
+      </c>
+      <c r="B11" t="n">
+        <v>158</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>181</v>
+      </c>
+      <c r="B13" t="n">
+        <v>181</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>183</v>
+      </c>
+      <c r="B14" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>208</v>
+      </c>
+      <c r="B16" t="n">
+        <v>208</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>247</v>
+      </c>
+      <c r="B19" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>eID_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>251</v>
+      </c>
+      <c r="B20" t="n">
+        <v>252</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>257</v>
+      </c>
+      <c r="B22" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>264</v>
+      </c>
+      <c r="B23" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>275</v>
+      </c>
+      <c r="B25" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="B26" t="n">
         <v>299.5</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>eID_2</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>eID_1</t>
         </is>
       </c>
     </row>

--- a/baselines/svm-baseline/detected_events.xlsx
+++ b/baselines/svm-baseline/detected_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,10 +435,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.5</v>
+        <v>61.05</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>67.55</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -448,49 +448,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>48.5</v>
+        <v>78.55</v>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>125.05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60</v>
+        <v>129.05</v>
       </c>
       <c r="B4" t="n">
-        <v>114.5</v>
+        <v>131.55</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117.5</v>
+        <v>152.55</v>
       </c>
       <c r="B5" t="n">
-        <v>118.5</v>
+        <v>158.05</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122</v>
+        <v>170.55</v>
       </c>
       <c r="B6" t="n">
-        <v>123.5</v>
+        <v>172.55</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -500,261 +500,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128.5</v>
+        <v>182.55</v>
       </c>
       <c r="B7" t="n">
-        <v>128.5</v>
+        <v>183.55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129</v>
+        <v>195.55</v>
       </c>
       <c r="B8" t="n">
-        <v>131.5</v>
+        <v>200.55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134.5</v>
+        <v>214.55</v>
       </c>
       <c r="B9" t="n">
-        <v>145.5</v>
+        <v>215.05</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>147.5</v>
+        <v>226.55</v>
       </c>
       <c r="B10" t="n">
-        <v>147.5</v>
+        <v>247.05</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>152</v>
-      </c>
-      <c r="B11" t="n">
-        <v>158</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="B12" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>181</v>
-      </c>
-      <c r="B13" t="n">
-        <v>181</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>183</v>
-      </c>
-      <c r="B14" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="B15" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>208</v>
-      </c>
-      <c r="B16" t="n">
-        <v>208</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>215.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>219</v>
-      </c>
-      <c r="B18" t="n">
-        <v>246.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>247</v>
-      </c>
-      <c r="B19" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>eID_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>251</v>
-      </c>
-      <c r="B20" t="n">
-        <v>252</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>252.5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>257</v>
-      </c>
-      <c r="B22" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>264</v>
-      </c>
-      <c r="B23" t="n">
-        <v>271.5</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>eID_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>273.5</v>
-      </c>
-      <c r="B24" t="n">
-        <v>273.5</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>eID_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>275</v>
-      </c>
-      <c r="B25" t="n">
-        <v>285.5</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>eID_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>294.5</v>
-      </c>
-      <c r="B26" t="n">
-        <v>299.5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>eID_1</t>
         </is>
       </c>
     </row>

--- a/baselines/svm-baseline/detected_events.xlsx
+++ b/baselines/svm-baseline/detected_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,118 +435,222 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61.05</v>
+        <v>1432.519</v>
       </c>
       <c r="B2" t="n">
-        <v>67.55</v>
+        <v>1440.019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78.55</v>
+        <v>1451.019</v>
       </c>
       <c r="B3" t="n">
-        <v>125.05</v>
+        <v>1452.019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129.05</v>
+        <v>1457.019</v>
       </c>
       <c r="B4" t="n">
-        <v>131.55</v>
+        <v>1463.519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>152.55</v>
+        <v>1467.519</v>
       </c>
       <c r="B5" t="n">
-        <v>158.05</v>
+        <v>1474.519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>412.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>170.55</v>
+        <v>1481.019</v>
       </c>
       <c r="B6" t="n">
-        <v>172.55</v>
+        <v>1490.519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>182.55</v>
+        <v>1496.019</v>
       </c>
       <c r="B7" t="n">
-        <v>183.55</v>
+        <v>1496.519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>406.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>195.55</v>
+        <v>1499.519</v>
       </c>
       <c r="B8" t="n">
-        <v>200.55</v>
+        <v>1500.019</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>214.55</v>
+        <v>1512.519</v>
       </c>
       <c r="B9" t="n">
-        <v>215.05</v>
+        <v>1513.019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>413.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>226.55</v>
+        <v>1518.019</v>
       </c>
       <c r="B10" t="n">
-        <v>247.05</v>
+        <v>1539.519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eID_5</t>
+          <t>405.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1541.019</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1542.019</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>412.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1542.519</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1544.019</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>413.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1554.519</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1567.019</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>405.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1569.019</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1570.019</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>406.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1574.519</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1575.019</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>405.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1584.019</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1589.019</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>404.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1630.019</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1631.019</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>413.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1657.519</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1658.519</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>413.0</t>
         </is>
       </c>
     </row>

--- a/baselines/svm-baseline/detected_events.xlsx
+++ b/baselines/svm-baseline/detected_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,222 +435,963 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1432.519</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1440.019</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1451.019</v>
+        <v>29.5</v>
       </c>
       <c r="B3" t="n">
-        <v>1452.019</v>
+        <v>36.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1457.019</v>
+        <v>58.5</v>
       </c>
       <c r="B4" t="n">
-        <v>1463.519</v>
+        <v>60.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1467.519</v>
+        <v>64.5</v>
       </c>
       <c r="B5" t="n">
-        <v>1474.519</v>
+        <v>65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1481.019</v>
+        <v>70.5</v>
       </c>
       <c r="B6" t="n">
-        <v>1490.519</v>
+        <v>75.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1496.019</v>
+        <v>79.5</v>
       </c>
       <c r="B7" t="n">
-        <v>1496.519</v>
+        <v>86.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>406.0</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1499.519</v>
+        <v>89.5</v>
       </c>
       <c r="B8" t="n">
-        <v>1500.019</v>
+        <v>95.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1512.519</v>
+        <v>96</v>
       </c>
       <c r="B9" t="n">
-        <v>1513.019</v>
+        <v>99.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1518.019</v>
+        <v>102</v>
       </c>
       <c r="B10" t="n">
-        <v>1539.519</v>
+        <v>102.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1541.019</v>
+        <v>106.5</v>
       </c>
       <c r="B11" t="n">
-        <v>1542.019</v>
+        <v>109</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>412.0</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1542.519</v>
+        <v>111</v>
       </c>
       <c r="B12" t="n">
-        <v>1544.019</v>
+        <v>112</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1554.519</v>
+        <v>116</v>
       </c>
       <c r="B13" t="n">
-        <v>1567.019</v>
+        <v>130.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1569.019</v>
+        <v>133.5</v>
       </c>
       <c r="B14" t="n">
-        <v>1570.019</v>
+        <v>134</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>406.0</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1574.519</v>
+        <v>137.5</v>
       </c>
       <c r="B15" t="n">
-        <v>1575.019</v>
+        <v>174.5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1584.019</v>
+        <v>176.5</v>
       </c>
       <c r="B16" t="n">
-        <v>1589.019</v>
+        <v>185.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>404.0</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1630.019</v>
+        <v>189</v>
       </c>
       <c r="B17" t="n">
-        <v>1631.019</v>
+        <v>190</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1657.519</v>
+        <v>195</v>
       </c>
       <c r="B18" t="n">
-        <v>1658.519</v>
+        <v>197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>206</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>215</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>238</v>
+      </c>
+      <c r="B23" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>242</v>
+      </c>
+      <c r="B24" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>250</v>
+      </c>
+      <c r="B25" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>273</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>283</v>
+      </c>
+      <c r="B27" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>303</v>
+      </c>
+      <c r="B29" t="n">
+        <v>311.5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>315</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="B31" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="B32" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>330</v>
+      </c>
+      <c r="B33" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>346</v>
+      </c>
+      <c r="B34" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>355</v>
+      </c>
+      <c r="B35" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="B36" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="B37" t="n">
+        <v>388</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="B38" t="n">
+        <v>394</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="B39" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>403</v>
+      </c>
+      <c r="B40" t="n">
+        <v>409</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>424</v>
+      </c>
+      <c r="B41" t="n">
+        <v>425.5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="B42" t="n">
+        <v>444</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="B43" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>453.5</v>
+      </c>
+      <c r="B44" t="n">
+        <v>454</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>457</v>
+      </c>
+      <c r="B45" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>473</v>
+      </c>
+      <c r="B46" t="n">
+        <v>479</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="B47" t="n">
+        <v>486</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="B48" t="n">
+        <v>493</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="B49" t="n">
+        <v>518</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>526</v>
+      </c>
+      <c r="B50" t="n">
+        <v>527</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>527.5</v>
+      </c>
+      <c r="B51" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>547</v>
+      </c>
+      <c r="B52" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>552</v>
+      </c>
+      <c r="B53" t="n">
+        <v>555</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>561</v>
+      </c>
+      <c r="B54" t="n">
+        <v>567.5</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="B55" t="n">
+        <v>595</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>601.5</v>
+      </c>
+      <c r="B56" t="n">
+        <v>622.5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>639</v>
+      </c>
+      <c r="B57" t="n">
+        <v>649</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>655</v>
+      </c>
+      <c r="B58" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>677.5</v>
+      </c>
+      <c r="B59" t="n">
+        <v>687</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>689.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>702</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>703.5</v>
+      </c>
+      <c r="B61" t="n">
+        <v>721</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>725.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>735.5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>750</v>
+      </c>
+      <c r="B63" t="n">
+        <v>750.5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>763</v>
+      </c>
+      <c r="B64" t="n">
+        <v>775</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>801</v>
+      </c>
+      <c r="B65" t="n">
+        <v>801.5</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>806.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>840</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>844.5</v>
+      </c>
+      <c r="B67" t="n">
+        <v>890.5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>891</v>
+      </c>
+      <c r="B68" t="n">
+        <v>891.5</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>894</v>
+      </c>
+      <c r="B69" t="n">
+        <v>894.5</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>898</v>
+      </c>
+      <c r="B70" t="n">
+        <v>909.5</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>911</v>
+      </c>
+      <c r="B71" t="n">
+        <v>913.5</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>eID_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="B72" t="n">
+        <v>941</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>943</v>
+      </c>
+      <c r="B73" t="n">
+        <v>961</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>961.5</v>
+      </c>
+      <c r="B74" t="n">
+        <v>962.5</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>963.5</v>
+      </c>
+      <c r="B75" t="n">
+        <v>991</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
